--- a/salidas/empresas/PNC.xlsx
+++ b/salidas/empresas/PNC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>35.97582244873047</v>
+        <v>35.975830078125</v>
       </c>
       <c r="C2" t="n">
         <v>64.86000061035156</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>39.02093887329102</v>
+        <v>39.02095413208008</v>
       </c>
       <c r="C3" t="n">
         <v>70.34999847412109</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>37.33474731445312</v>
+        <v>37.33475112915039</v>
       </c>
       <c r="C4" t="n">
         <v>67.30999755859375</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>38.53838348388672</v>
+        <v>38.53841018676758</v>
       </c>
       <c r="C6" t="n">
         <v>68.91000366210938</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>39.24305725097656</v>
+        <v>39.24304580688477</v>
       </c>
       <c r="C7" t="n">
         <v>70.16999816894531</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>39.92813873291016</v>
+        <v>39.92816925048828</v>
       </c>
       <c r="C8" t="n">
         <v>70.83999633789062</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.82998657226562</v>
+        <v>40.82997512817383</v>
       </c>
       <c r="C10" t="n">
         <v>72.44000244140625</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>39.78302001953125</v>
+        <v>39.78303146362305</v>
       </c>
       <c r="C11" t="n">
         <v>70.02999877929688</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>40.15796661376953</v>
+        <v>40.1579704284668</v>
       </c>
       <c r="C12" t="n">
         <v>70.69000244140625</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>42.06105804443359</v>
+        <v>42.06106948852539</v>
       </c>
       <c r="C13" t="n">
         <v>74.04000091552734</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.21681213378906</v>
+        <v>42.21682357788086</v>
       </c>
       <c r="C14" t="n">
         <v>73.76999664306641</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>41.94211959838867</v>
+        <v>41.94211578369141</v>
       </c>
       <c r="C15" t="n">
         <v>73.29000091552734</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>42.77543258666992</v>
+        <v>42.77543640136719</v>
       </c>
       <c r="C17" t="n">
         <v>74.09999847412109</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>41.32072067260742</v>
+        <v>41.32071304321289</v>
       </c>
       <c r="C19" t="n">
         <v>71.58000183105469</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>38.81691741943359</v>
+        <v>38.81690979003906</v>
       </c>
       <c r="C20" t="n">
         <v>66.65000152587891</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>40.98342895507812</v>
+        <v>40.98343276977539</v>
       </c>
       <c r="C21" t="n">
         <v>70.37000274658203</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>39.66141128540039</v>
+        <v>39.66139602661133</v>
       </c>
       <c r="C22" t="n">
         <v>68.09999847412109</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>42.39911651611328</v>
+        <v>42.39910888671875</v>
       </c>
       <c r="C23" t="n">
         <v>72.16000366210938</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>43.01604843139648</v>
+        <v>43.01605606079102</v>
       </c>
       <c r="C24" t="n">
         <v>73.20999908447266</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>38.57401275634766</v>
+        <v>38.57401657104492</v>
       </c>
       <c r="C25" t="n">
         <v>65.65000152587891</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>36.46816635131836</v>
+        <v>36.46815872192383</v>
       </c>
       <c r="C27" t="n">
         <v>61.43000030517578</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>38.92588424682617</v>
+        <v>38.92588806152344</v>
       </c>
       <c r="C28" t="n">
         <v>65.56999969482422</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>41.58499145507812</v>
+        <v>41.58499908447266</v>
       </c>
       <c r="C29" t="n">
         <v>69.34999847412109</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>38.52682876586914</v>
+        <v>38.52684020996094</v>
       </c>
       <c r="C30" t="n">
         <v>64.25</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>34.23941802978516</v>
+        <v>34.23943328857422</v>
       </c>
       <c r="C31" t="n">
         <v>57.09999847412109</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>43.23686981201172</v>
+        <v>43.23685455322266</v>
       </c>
       <c r="C32" t="n">
         <v>71.29000091552734</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>43.63713455200195</v>
+        <v>43.63714981079102</v>
       </c>
       <c r="C33" t="n">
         <v>71.94999694824219</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>45.30501174926758</v>
+        <v>45.30499267578125</v>
       </c>
       <c r="C34" t="n">
         <v>74.69999694824219</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>32.31234741210938</v>
+        <v>32.31235504150391</v>
       </c>
       <c r="C36" t="n">
         <v>52.77000045776367</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>30.00388526916504</v>
+        <v>30.00389099121094</v>
       </c>
       <c r="C37" t="n">
         <v>49</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>16.98452949523926</v>
+        <v>16.98453140258789</v>
       </c>
       <c r="C39" t="n">
         <v>27.34000015258789</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>18.1959342956543</v>
+        <v>18.19593811035156</v>
       </c>
       <c r="C40" t="n">
         <v>29.29000091552734</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>24.74084663391113</v>
+        <v>24.74084854125977</v>
       </c>
       <c r="C41" t="n">
         <v>39.70000076293945</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>28.38654708862305</v>
+        <v>28.38654899597168</v>
       </c>
       <c r="C42" t="n">
         <v>45.54999923706055</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>24.18621253967285</v>
+        <v>24.18621635437012</v>
       </c>
       <c r="C43" t="n">
         <v>38.81000137329102</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.90936660766602</v>
+        <v>22.90937232971191</v>
       </c>
       <c r="C44" t="n">
         <v>36.65999984741211</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>30.36459350585938</v>
+        <v>30.3646068572998</v>
       </c>
       <c r="C46" t="n">
         <v>48.59000015258789</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>30.65033721923828</v>
+        <v>30.65033531188965</v>
       </c>
       <c r="C47" t="n">
         <v>48.93999862670898</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>35.70444107055664</v>
+        <v>35.70445251464844</v>
       </c>
       <c r="C48" t="n">
         <v>57.0099983215332</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.06151580810547</v>
+        <v>33.0615348815918</v>
       </c>
       <c r="C49" t="n">
         <v>52.79000091552734</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>34.7762451171875</v>
+        <v>34.77624893188477</v>
       </c>
       <c r="C50" t="n">
         <v>55.43000030517578</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>37.45521545410156</v>
+        <v>37.45519638061523</v>
       </c>
       <c r="C52" t="n">
         <v>59.70000076293945</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>42.23280715942383</v>
+        <v>42.2327995300293</v>
       </c>
       <c r="C53" t="n">
         <v>67.20999908447266</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>39.43026733398438</v>
+        <v>39.43027496337891</v>
       </c>
       <c r="C54" t="n">
         <v>62.75</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>35.50293731689453</v>
+        <v>35.50295639038086</v>
       </c>
       <c r="C55" t="n">
         <v>56.5</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>37.37932968139648</v>
+        <v>37.37933349609375</v>
       </c>
       <c r="C56" t="n">
         <v>59.38999938964844</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>32.09248733520508</v>
+        <v>32.09247589111328</v>
       </c>
       <c r="C57" t="n">
         <v>50.9900016784668</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>32.67152404785156</v>
+        <v>32.67151260375977</v>
       </c>
       <c r="C58" t="n">
         <v>51.90999984741211</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>33.98806381225586</v>
+        <v>33.98807144165039</v>
       </c>
       <c r="C59" t="n">
         <v>53.90000152587891</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>33.95653533935547</v>
+        <v>33.95653915405273</v>
       </c>
       <c r="C60" t="n">
         <v>53.84999847412109</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>38.28859710693359</v>
+        <v>38.28859329223633</v>
       </c>
       <c r="C61" t="n">
         <v>60.72000122070312</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>37.89597702026367</v>
+        <v>37.89598083496094</v>
       </c>
       <c r="C62" t="n">
         <v>60</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>38.96971130371094</v>
+        <v>38.96969985961914</v>
       </c>
       <c r="C63" t="n">
         <v>61.70000076293945</v>
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>39.78445816040039</v>
+        <v>39.78446197509766</v>
       </c>
       <c r="C64" t="n">
         <v>62.9900016784668</v>
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>39.59552764892578</v>
+        <v>39.59551620483398</v>
       </c>
       <c r="C65" t="n">
         <v>62.34000015258789</v>
@@ -1832,7 +1844,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1890,11 +1902,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>34.69184112548828</v>
+        <v>34.69182968139648</v>
       </c>
       <c r="C68" t="n">
         <v>54.29000091552734</v>
@@ -1919,11 +1931,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>32.03995513916016</v>
+        <v>32.03995895385742</v>
       </c>
       <c r="C69" t="n">
         <v>50.13999938964844</v>
@@ -1948,11 +1960,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>30.79387283325195</v>
+        <v>30.79387855529785</v>
       </c>
       <c r="C70" t="n">
         <v>48.18999862670898</v>
@@ -1977,11 +1989,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>34.55763244628906</v>
+        <v>34.5576286315918</v>
       </c>
       <c r="C71" t="n">
         <v>53.70999908447266</v>
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>34.87935256958008</v>
+        <v>34.87934494018555</v>
       </c>
       <c r="C72" t="n">
         <v>54.20999908447266</v>
@@ -2035,11 +2047,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>37.10552978515625</v>
+        <v>37.10553741455078</v>
       </c>
       <c r="C73" t="n">
         <v>57.66999816894531</v>
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>38.12624740600586</v>
+        <v>38.12625885009766</v>
       </c>
       <c r="C74" t="n">
         <v>58.91999816894531</v>
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>38.51449966430664</v>
+        <v>38.51451873779297</v>
       </c>
       <c r="C75" t="n">
         <v>59.52000045776367</v>
@@ -2122,11 +2134,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>41.73051452636719</v>
+        <v>41.73052215576172</v>
       </c>
       <c r="C76" t="n">
         <v>64.48999786376953</v>
@@ -2151,11 +2163,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>43.18711853027344</v>
+        <v>43.18710708618164</v>
       </c>
       <c r="C77" t="n">
         <v>66.31999969482422</v>
@@ -2180,11 +2192,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>39.99625778198242</v>
+        <v>39.99626922607422</v>
       </c>
       <c r="C78" t="n">
         <v>61.41999816894531</v>
@@ -2209,11 +2221,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>39.79440689086914</v>
+        <v>39.79439926147461</v>
       </c>
       <c r="C79" t="n">
         <v>61.11000061035156</v>
@@ -2238,11 +2250,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>38.74228286743164</v>
+        <v>38.74227523803711</v>
       </c>
       <c r="C80" t="n">
         <v>59.09999847412109</v>
@@ -2267,11 +2279,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>40.74822235107422</v>
+        <v>40.74822998046875</v>
       </c>
       <c r="C81" t="n">
         <v>62.15999984741211</v>
@@ -2296,11 +2308,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>41.36442565917969</v>
+        <v>41.36443328857422</v>
       </c>
       <c r="C82" t="n">
         <v>63.09999847412109</v>
@@ -2325,11 +2337,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>38.38873672485352</v>
+        <v>38.38872528076172</v>
       </c>
       <c r="C83" t="n">
         <v>58.20000076293945</v>
@@ -2354,11 +2366,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>37.02994537353516</v>
+        <v>37.02993774414062</v>
       </c>
       <c r="C84" t="n">
         <v>56.13999938964844</v>
@@ -2383,11 +2395,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>38.46127700805664</v>
+        <v>38.46128082275391</v>
       </c>
       <c r="C85" t="n">
         <v>58.31000137329102</v>
@@ -2412,7 +2424,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2441,11 +2453,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.42345428466797</v>
+        <v>41.42345809936523</v>
       </c>
       <c r="C87" t="n">
         <v>62.38999938964844</v>
@@ -2470,11 +2482,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>44.15225601196289</v>
+        <v>44.15225219726562</v>
       </c>
       <c r="C88" t="n">
         <v>66.5</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>45.36504364013672</v>
+        <v>45.36505126953125</v>
       </c>
       <c r="C89" t="n">
         <v>67.87999725341797</v>
@@ -2528,11 +2540,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>47.87791442871094</v>
+        <v>47.87790298461914</v>
       </c>
       <c r="C90" t="n">
         <v>71.63999938964844</v>
@@ -2557,11 +2569,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>48.73335266113281</v>
+        <v>48.73334884643555</v>
       </c>
       <c r="C91" t="n">
         <v>72.91999816894531</v>
@@ -2586,11 +2598,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>51.12678527832031</v>
+        <v>51.12676239013672</v>
       </c>
       <c r="C92" t="n">
         <v>76.05000305175781</v>
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>48.58554458618164</v>
+        <v>48.58554840087891</v>
       </c>
       <c r="C93" t="n">
         <v>72.26999664306641</v>
@@ -2644,11 +2656,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>48.70656204223633</v>
+        <v>48.70655822753906</v>
       </c>
       <c r="C94" t="n">
         <v>72.44999694824219</v>
@@ -2673,11 +2685,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>49.74144744873047</v>
+        <v>49.7414436340332</v>
       </c>
       <c r="C95" t="n">
         <v>73.52999877929688</v>
@@ -2702,7 +2714,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2731,7 +2743,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2760,11 +2772,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>54.34060287475586</v>
+        <v>54.34062576293945</v>
       </c>
       <c r="C98" t="n">
         <v>79.87999725341797</v>
@@ -2789,11 +2801,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>55.63314819335938</v>
+        <v>55.63314437866211</v>
       </c>
       <c r="C99" t="n">
         <v>81.77999877929688</v>
@@ -2818,7 +2830,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2847,11 +2859,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>57.50632858276367</v>
+        <v>57.50634765625</v>
       </c>
       <c r="C101" t="n">
         <v>84.04000091552734</v>
@@ -2876,11 +2888,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>58.34799194335938</v>
+        <v>58.34800338745117</v>
       </c>
       <c r="C102" t="n">
         <v>85.26999664306641</v>
@@ -2905,11 +2917,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>60.93454360961914</v>
+        <v>60.93454742431641</v>
       </c>
       <c r="C103" t="n">
         <v>89.05000305175781</v>
@@ -2934,11 +2946,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>56.80541229248047</v>
+        <v>56.8054084777832</v>
       </c>
       <c r="C104" t="n">
         <v>82.55999755859375</v>
@@ -2963,11 +2975,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>58.31225204467773</v>
+        <v>58.31223678588867</v>
       </c>
       <c r="C105" t="n">
         <v>84.75</v>
@@ -2992,11 +3004,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>58.88332366943359</v>
+        <v>58.8832893371582</v>
       </c>
       <c r="C106" t="n">
         <v>85.58000183105469</v>
@@ -3021,11 +3033,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>59.78630447387695</v>
+        <v>59.78631591796875</v>
       </c>
       <c r="C107" t="n">
         <v>86.38999938964844</v>
@@ -3050,11 +3062,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>60.53373718261719</v>
+        <v>60.53371047973633</v>
       </c>
       <c r="C108" t="n">
         <v>87.47000122070312</v>
@@ -3079,11 +3091,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>63.13585662841797</v>
+        <v>63.1358528137207</v>
       </c>
       <c r="C109" t="n">
         <v>91.23000335693359</v>
@@ -3108,11 +3120,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>58.83378601074219</v>
+        <v>58.83378219604492</v>
       </c>
       <c r="C110" t="n">
         <v>84.54000091552734</v>
@@ -3137,11 +3149,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>63.99758148193359</v>
+        <v>63.9975700378418</v>
       </c>
       <c r="C111" t="n">
         <v>91.95999908447266</v>
@@ -3166,11 +3178,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>64.88835906982422</v>
+        <v>64.88835144042969</v>
       </c>
       <c r="C112" t="n">
         <v>93.23999786376953</v>
@@ -3195,11 +3207,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>64.18769073486328</v>
+        <v>64.18768310546875</v>
       </c>
       <c r="C113" t="n">
         <v>91.73000335693359</v>
@@ -3224,11 +3236,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>66.95867156982422</v>
+        <v>66.95867919921875</v>
       </c>
       <c r="C114" t="n">
         <v>95.69000244140625</v>
@@ -3253,11 +3265,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>66.93069458007812</v>
+        <v>66.93070220947266</v>
       </c>
       <c r="C115" t="n">
         <v>95.65000152587891</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>69.06681060791016</v>
+        <v>69.06681823730469</v>
       </c>
       <c r="C116" t="n">
         <v>98.18000030517578</v>
@@ -3311,11 +3323,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>64.10032653808594</v>
+        <v>64.10031127929688</v>
       </c>
       <c r="C117" t="n">
         <v>91.12000274658203</v>
@@ -3340,11 +3352,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>62.74965286254883</v>
+        <v>62.74966049194336</v>
       </c>
       <c r="C118" t="n">
         <v>89.19999694824219</v>
@@ -3369,11 +3381,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>63.85836410522461</v>
+        <v>63.85835266113281</v>
       </c>
       <c r="C119" t="n">
         <v>90.26000213623047</v>
@@ -3398,11 +3410,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>67.57270050048828</v>
+        <v>67.57270812988281</v>
       </c>
       <c r="C120" t="n">
         <v>95.51000213623047</v>
@@ -3427,11 +3439,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>67.43119812011719</v>
+        <v>67.43121337890625</v>
       </c>
       <c r="C121" t="n">
         <v>95.30999755859375</v>
@@ -3456,11 +3468,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>61.66831207275391</v>
+        <v>61.66830444335938</v>
       </c>
       <c r="C122" t="n">
         <v>86.65000152587891</v>
@@ -3485,11 +3497,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>57.86782836914062</v>
+        <v>57.86784744262695</v>
       </c>
       <c r="C123" t="n">
         <v>81.30999755859375</v>
@@ -3514,11 +3526,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>60.1879768371582</v>
+        <v>60.18795776367188</v>
       </c>
       <c r="C124" t="n">
         <v>84.56999969482422</v>
@@ -3543,7 +3555,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3572,7 +3584,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3601,11 +3613,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>58.28352355957031</v>
+        <v>58.28352737426758</v>
       </c>
       <c r="C127" t="n">
         <v>81.38999938964844</v>
@@ -3630,11 +3642,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>59.58495330810547</v>
+        <v>59.5849609375</v>
       </c>
       <c r="C128" t="n">
         <v>82.65000152587891</v>
@@ -3659,11 +3671,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>64.95590972900391</v>
+        <v>64.95589447021484</v>
       </c>
       <c r="C129" t="n">
         <v>90.09999847412109</v>
@@ -3688,7 +3700,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3717,11 +3729,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>69.34299468994141</v>
+        <v>69.34300231933594</v>
       </c>
       <c r="C131" t="n">
         <v>95.59999847412109</v>
@@ -3746,11 +3758,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>80.17964172363281</v>
+        <v>80.17965698242188</v>
       </c>
       <c r="C132" t="n">
         <v>110.5400009155273</v>
@@ -3775,11 +3787,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>84.83639526367188</v>
+        <v>84.83637237548828</v>
       </c>
       <c r="C133" t="n">
         <v>116.9599990844727</v>
@@ -3804,11 +3816,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>87.77296447753906</v>
+        <v>87.77299499511719</v>
       </c>
       <c r="C134" t="n">
         <v>120.4599990844727</v>
@@ -3833,11 +3845,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>92.7059326171875</v>
+        <v>92.70590972900391</v>
       </c>
       <c r="C135" t="n">
         <v>127.2300033569336</v>
@@ -3862,11 +3874,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>87.6126708984375</v>
+        <v>87.61265563964844</v>
       </c>
       <c r="C136" t="n">
         <v>120.2399978637695</v>
@@ -3891,11 +3903,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>87.66412353515625</v>
+        <v>87.66413879394531</v>
       </c>
       <c r="C137" t="n">
         <v>119.75</v>
@@ -3920,11 +3932,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>86.89546203613281</v>
+        <v>86.89546966552734</v>
       </c>
       <c r="C138" t="n">
         <v>118.6999969482422</v>
@@ -3949,11 +3961,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>91.41226959228516</v>
+        <v>91.41228485107422</v>
       </c>
       <c r="C139" t="n">
         <v>124.870002746582</v>
@@ -3978,7 +3990,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4007,7 +4019,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4036,11 +4048,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>99.24473571777344</v>
+        <v>99.2447509765625</v>
       </c>
       <c r="C142" t="n">
         <v>134.7700042724609</v>
@@ -4065,11 +4077,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>101.3003005981445</v>
+        <v>101.3002853393555</v>
       </c>
       <c r="C143" t="n">
         <v>136.7899932861328</v>
@@ -4094,11 +4106,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>104.0921936035156</v>
+        <v>104.0921859741211</v>
       </c>
       <c r="C144" t="n">
         <v>140.5599975585938</v>
@@ -4123,11 +4135,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>106.8544387817383</v>
+        <v>106.8544769287109</v>
       </c>
       <c r="C145" t="n">
         <v>144.2899932861328</v>
@@ -4152,11 +4164,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>117.6031875610352</v>
+        <v>117.6031646728516</v>
       </c>
       <c r="C146" t="n">
         <v>158.0200042724609</v>
@@ -4181,7 +4193,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4210,11 +4222,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>112.5573272705078</v>
+        <v>112.5572662353516</v>
       </c>
       <c r="C148" t="n">
         <v>151.2400054931641</v>
@@ -4239,11 +4251,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>108.9029083251953</v>
+        <v>108.9029006958008</v>
       </c>
       <c r="C149" t="n">
         <v>145.6100006103516</v>
@@ -4268,11 +4280,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>107.2574615478516</v>
+        <v>107.2574996948242</v>
       </c>
       <c r="C150" t="n">
         <v>143.4100036621094</v>
@@ -4297,11 +4309,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>101.042366027832</v>
+        <v>101.0423889160156</v>
       </c>
       <c r="C151" t="n">
         <v>135.1000061035156</v>
@@ -4326,11 +4338,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>109.0685882568359</v>
+        <v>109.0686187744141</v>
       </c>
       <c r="C152" t="n">
         <v>144.8300018310547</v>
@@ -4355,11 +4367,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>108.0971603393555</v>
+        <v>108.0971298217773</v>
       </c>
       <c r="C153" t="n">
         <v>143.5399932861328</v>
@@ -4384,11 +4396,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>102.56201171875</v>
+        <v>102.5620040893555</v>
       </c>
       <c r="C154" t="n">
         <v>136.1900024414062</v>
@@ -4413,11 +4425,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>97.50076293945312</v>
+        <v>97.50075531005859</v>
       </c>
       <c r="C155" t="n">
         <v>128.4900054931641</v>
@@ -4442,7 +4454,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4471,11 +4483,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>88.71361541748047</v>
+        <v>88.71363067626953</v>
       </c>
       <c r="C157" t="n">
         <v>116.9100036621094</v>
@@ -4500,11 +4512,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>93.82029724121094</v>
+        <v>93.82028961181641</v>
       </c>
       <c r="C158" t="n">
         <v>122.6699981689453</v>
@@ -4529,11 +4541,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>96.38242340087891</v>
+        <v>96.38246154785156</v>
       </c>
       <c r="C159" t="n">
         <v>126.0199966430664</v>
@@ -4558,11 +4570,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>93.81265258789062</v>
+        <v>93.81266021728516</v>
       </c>
       <c r="C160" t="n">
         <v>122.6600036621094</v>
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4616,7 +4628,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4645,11 +4657,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>105.7513656616211</v>
+        <v>105.7513580322266</v>
       </c>
       <c r="C163" t="n">
         <v>137.2799987792969</v>
@@ -4674,11 +4686,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>110.9944763183594</v>
+        <v>110.9944686889648</v>
       </c>
       <c r="C164" t="n">
         <v>142.8999938964844</v>
@@ -4703,7 +4715,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4732,11 +4744,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>108.8662414550781</v>
+        <v>108.8662643432617</v>
       </c>
       <c r="C166" t="n">
         <v>140.1600036621094</v>
@@ -4761,7 +4773,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4790,11 +4802,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>119.9750595092773</v>
+        <v>119.9750518798828</v>
       </c>
       <c r="C168" t="n">
         <v>153.2100067138672</v>
@@ -4819,11 +4831,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>125.0024032592773</v>
+        <v>125.00244140625</v>
       </c>
       <c r="C169" t="n">
         <v>159.6300048828125</v>
@@ -4848,11 +4860,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>117.2006988525391</v>
+        <v>117.2006607055664</v>
       </c>
       <c r="C170" t="n">
         <v>148.5500030517578</v>
@@ -4877,11 +4889,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>99.72511291503906</v>
+        <v>99.72512054443359</v>
       </c>
       <c r="C171" t="n">
         <v>126.4000015258789</v>
@@ -4906,11 +4918,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>75.51969146728516</v>
+        <v>75.51968383789062</v>
       </c>
       <c r="C172" t="n">
         <v>95.72000122070312</v>
@@ -4935,7 +4947,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4964,7 +4976,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4993,11 +5005,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>83.97785186767578</v>
+        <v>83.97784423828125</v>
       </c>
       <c r="C175" t="n">
         <v>105.2099990844727</v>
@@ -5022,11 +5034,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>86.09455108642578</v>
+        <v>86.09456634521484</v>
       </c>
       <c r="C176" t="n">
         <v>106.6699981689453</v>
@@ -5051,11 +5063,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>89.75077819824219</v>
+        <v>89.75079345703125</v>
       </c>
       <c r="C177" t="n">
         <v>111.1999969482422</v>
@@ -5080,7 +5092,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5109,11 +5121,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>91.25511169433594</v>
+        <v>91.255126953125</v>
       </c>
       <c r="C179" t="n">
         <v>111.879997253418</v>
@@ -5138,11 +5150,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>112.6170425415039</v>
+        <v>112.6170501708984</v>
       </c>
       <c r="C180" t="n">
         <v>138.0700073242188</v>
@@ -5167,11 +5179,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>121.5321197509766</v>
+        <v>121.5320816040039</v>
       </c>
       <c r="C181" t="n">
         <v>149</v>
@@ -5196,11 +5208,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>117.9018859863281</v>
+        <v>117.9019241333008</v>
       </c>
       <c r="C182" t="n">
         <v>143.5200042724609</v>
@@ -5225,11 +5237,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>138.3080139160156</v>
+        <v>138.3079833984375</v>
       </c>
       <c r="C183" t="n">
         <v>168.3600006103516</v>
@@ -5254,11 +5266,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>144.0995941162109</v>
+        <v>144.0995635986328</v>
       </c>
       <c r="C184" t="n">
         <v>175.4100036621094</v>
@@ -5283,7 +5295,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5312,7 +5324,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5341,11 +5353,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>157.7210083007812</v>
+        <v>157.7209930419922</v>
       </c>
       <c r="C187" t="n">
         <v>190.7599945068359</v>
@@ -5370,11 +5382,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>151.8248291015625</v>
+        <v>151.8248596191406</v>
       </c>
       <c r="C188" t="n">
         <v>182.4100036621094</v>
@@ -5399,11 +5411,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>159.0577392578125</v>
+        <v>159.0577697753906</v>
       </c>
       <c r="C189" t="n">
         <v>191.1000061035156</v>
@@ -5428,11 +5440,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>162.8365325927734</v>
+        <v>162.8365631103516</v>
       </c>
       <c r="C190" t="n">
         <v>195.6399993896484</v>
@@ -5457,11 +5469,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>176.7410430908203</v>
+        <v>176.7410278320312</v>
       </c>
       <c r="C191" t="n">
         <v>211.0299987792969</v>
@@ -5486,11 +5498,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>164.9906616210938</v>
+        <v>164.9906768798828</v>
       </c>
       <c r="C192" t="n">
         <v>197</v>
@@ -5515,11 +5527,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>167.9387359619141</v>
+        <v>167.9387512207031</v>
       </c>
       <c r="C193" t="n">
         <v>200.5200042724609</v>
@@ -5544,7 +5556,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5573,11 +5585,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>167.8013763427734</v>
+        <v>167.8013458251953</v>
       </c>
       <c r="C195" t="n">
         <v>199.25</v>
@@ -5602,11 +5614,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>155.3373565673828</v>
+        <v>155.3373260498047</v>
       </c>
       <c r="C196" t="n">
         <v>184.4499969482422</v>
@@ -5631,7 +5643,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5660,7 +5672,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5689,11 +5701,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>133.9606018066406</v>
+        <v>133.9605712890625</v>
       </c>
       <c r="C199" t="n">
         <v>157.7700042724609</v>
@@ -5718,11 +5730,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>142.2291564941406</v>
+        <v>142.2291259765625</v>
       </c>
       <c r="C200" t="n">
         <v>165.9400024414062</v>
@@ -5747,7 +5759,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5776,7 +5788,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5805,11 +5817,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>140.0800476074219</v>
+        <v>140.0800323486328</v>
       </c>
       <c r="C203" t="n">
         <v>161.8300018310547</v>
@@ -5834,11 +5846,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>145.6458435058594</v>
+        <v>145.6458282470703</v>
       </c>
       <c r="C204" t="n">
         <v>168.2599945068359</v>
@@ -5863,11 +5875,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>136.7128448486328</v>
+        <v>136.7128753662109</v>
       </c>
       <c r="C205" t="n">
         <v>157.9400024414062</v>
@@ -5892,11 +5904,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>144.4799499511719</v>
+        <v>144.4799041748047</v>
       </c>
       <c r="C206" t="n">
         <v>165.4299926757812</v>
@@ -5921,11 +5933,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>137.9210052490234</v>
+        <v>137.9209899902344</v>
       </c>
       <c r="C207" t="n">
         <v>157.9199981689453</v>
@@ -5950,11 +5962,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>111.004035949707</v>
+        <v>111.0040435791016</v>
       </c>
       <c r="C208" t="n">
         <v>127.0999984741211</v>
@@ -5979,11 +5991,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>115.1729125976562</v>
+        <v>115.1729354858398</v>
       </c>
       <c r="C209" t="n">
         <v>130.25</v>
@@ -6008,11 +6020,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>102.4221038818359</v>
+        <v>102.422119140625</v>
       </c>
       <c r="C210" t="n">
         <v>115.8300018310547</v>
@@ -6037,11 +6049,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>111.3706817626953</v>
+        <v>111.3706741333008</v>
       </c>
       <c r="C211" t="n">
         <v>125.9499969482422</v>
@@ -6066,11 +6078,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>122.5073318481445</v>
+        <v>122.5073547363281</v>
       </c>
       <c r="C212" t="n">
         <v>136.8899993896484</v>
@@ -6095,11 +6107,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>108.0452346801758</v>
+        <v>108.0452423095703</v>
       </c>
       <c r="C213" t="n">
         <v>120.7300033569336</v>
@@ -6124,11 +6136,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>109.8708877563477</v>
+        <v>109.8708801269531</v>
       </c>
       <c r="C214" t="n">
         <v>122.7699966430664</v>
@@ -6153,11 +6165,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>103.8048934936523</v>
+        <v>103.8048782348633</v>
       </c>
       <c r="C215" t="n">
         <v>114.4700012207031</v>
@@ -6182,11 +6194,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>121.47900390625</v>
+        <v>121.4790191650391</v>
       </c>
       <c r="C216" t="n">
         <v>133.9600067138672</v>
@@ -6211,11 +6223,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>140.4227142333984</v>
+        <v>140.4226989746094</v>
       </c>
       <c r="C217" t="n">
         <v>154.8500061035156</v>
@@ -6240,7 +6252,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6269,11 +6281,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>134.8557586669922</v>
+        <v>134.8557434082031</v>
       </c>
       <c r="C219" t="n">
         <v>147.1999969482422</v>
@@ -6298,11 +6310,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>148.0481872558594</v>
+        <v>148.0481414794922</v>
       </c>
       <c r="C220" t="n">
         <v>161.6000061035156</v>
@@ -6327,11 +6339,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>141.8343658447266</v>
+        <v>141.8343505859375</v>
       </c>
       <c r="C221" t="n">
         <v>153.2599945068359</v>
@@ -6356,7 +6368,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6385,7 +6397,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6414,11 +6426,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>169.2050018310547</v>
+        <v>169.2049865722656</v>
       </c>
       <c r="C224" t="n">
         <v>181.1000061035156</v>
@@ -6443,7 +6455,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6472,11 +6484,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>172.7087097167969</v>
+        <v>172.7086944580078</v>
       </c>
       <c r="C226" t="n">
         <v>184.8500061035156</v>
@@ -6501,11 +6513,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>177.3796081542969</v>
+        <v>177.3796234130859</v>
       </c>
       <c r="C227" t="n">
         <v>188.2700042724609</v>
@@ -6530,7 +6542,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6559,11 +6571,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>181.6947021484375</v>
+        <v>181.6946716308594</v>
       </c>
       <c r="C229" t="n">
         <v>192.8500061035156</v>
@@ -6588,11 +6600,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>190.88671875</v>
+        <v>190.8867034912109</v>
       </c>
       <c r="C230" t="n">
         <v>200.9499969482422</v>
@@ -6617,7 +6629,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6646,11 +6658,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>166.9676818847656</v>
+        <v>166.9676971435547</v>
       </c>
       <c r="C232" t="n">
         <v>175.7700042724609</v>
@@ -6675,7 +6687,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6704,7 +6716,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6733,7 +6745,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6762,7 +6774,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6791,7 +6803,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6820,7 +6832,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6849,11 +6861,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>178.3564758300781</v>
+        <v>178.3564910888672</v>
       </c>
       <c r="C239" t="n">
         <v>182.5500030517578</v>
@@ -6878,7 +6890,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6907,7 +6919,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6936,11 +6948,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>219.844970703125</v>
+        <v>219.8449859619141</v>
       </c>
       <c r="C242" t="n">
         <v>223.3000030517578</v>
@@ -6965,11 +6977,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>209.0644073486328</v>
+        <v>209.0644226074219</v>
       </c>
       <c r="C243" t="n">
         <v>212.3500061035156</v>
@@ -6994,7 +7006,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7023,7 +7035,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7052,7 +7064,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7081,7 +7093,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7110,7 +7122,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7139,7 +7151,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7168,32 +7180,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>224.0299987792969</v>
+        <v>223.3399963378906</v>
       </c>
       <c r="C250" t="n">
-        <v>224.0299987792969</v>
+        <v>223.3399963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>27141500</v>
+        <v>28865100</v>
       </c>
       <c r="E250" t="n">
         <v>18.17</v>
       </c>
       <c r="F250" t="n">
-        <v>12.32966421460082</v>
+        <v>12.29168939669183</v>
       </c>
       <c r="G250" t="n">
         <v>398943667</v>
       </c>
       <c r="H250" t="n">
-        <v>89375349231.01822</v>
+        <v>89100077126.80466</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06803341485302987</v>
+        <v>0.07235382433079204</v>
       </c>
     </row>
   </sheetData>
@@ -7225,75 +7237,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7329,13 +7341,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7371,13 +7383,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7413,13 +7425,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7539,13 +7551,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7623,13 +7635,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7656,7 +7668,7 @@
       <c r="I10" t="n">
         <v>5.74</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="K10" t="n">
@@ -7669,13 +7681,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40542</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7702,7 +7714,7 @@
       <c r="I11" t="n">
         <v>6.65</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K11" t="n">
@@ -7715,13 +7727,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7748,7 +7760,7 @@
       <c r="I12" t="n">
         <v>6.850000000000001</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="K12" t="n">
@@ -7761,13 +7773,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7794,7 +7806,7 @@
       <c r="I13" t="n">
         <v>6.330000000000002</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="K13" t="n">
@@ -7807,13 +7819,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7840,7 +7852,7 @@
       <c r="I14" t="n">
         <v>5.640000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K14" t="n">
@@ -7853,13 +7865,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7886,7 +7898,7 @@
       <c r="I15" t="n">
         <v>5.51</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="K15" t="n">
@@ -7899,13 +7911,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7932,7 +7944,7 @@
       <c r="I16" t="n">
         <v>4.82</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K16" t="n">
@@ -7945,13 +7957,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7978,7 +7990,7 @@
       <c r="I17" t="n">
         <v>4.909999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="K17" t="n">
@@ -7991,13 +8003,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8024,7 +8036,7 @@
       <c r="I18" t="n">
         <v>5.3</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K18" t="n">
@@ -8037,13 +8049,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8070,7 +8082,7 @@
       <c r="I19" t="n">
         <v>5.62</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="K19" t="n">
@@ -8083,13 +8095,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8116,7 +8128,7 @@
       <c r="I20" t="n">
         <v>6.630000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K20" t="n">
@@ -8129,13 +8141,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8162,7 +8174,7 @@
       <c r="I21" t="n">
         <v>6.78</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K21" t="n">
@@ -8175,13 +8187,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8208,7 +8220,7 @@
       <c r="I22" t="n">
         <v>7.39</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="K22" t="n">
@@ -8221,13 +8233,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8254,7 +8266,7 @@
       <c r="I23" t="n">
         <v>7.449999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K23" t="n">
@@ -8267,13 +8279,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8300,7 +8312,7 @@
       <c r="I24" t="n">
         <v>7.31</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="K24" t="n">
@@ -8313,13 +8325,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8346,7 +8358,7 @@
       <c r="I25" t="n">
         <v>7.31</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K25" t="n">
@@ -8359,13 +8371,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8392,7 +8404,7 @@
       <c r="I26" t="n">
         <v>7.3</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="K26" t="n">
@@ -8405,13 +8417,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8438,7 +8450,7 @@
       <c r="I27" t="n">
         <v>7.23</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K27" t="n">
@@ -8451,13 +8463,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8484,7 +8496,7 @@
       <c r="I28" t="n">
         <v>7.26</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K28" t="n">
@@ -8497,13 +8509,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8530,7 +8542,7 @@
       <c r="I29" t="n">
         <v>7.369999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K29" t="n">
@@ -8543,13 +8555,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8576,7 +8588,7 @@
       <c r="I30" t="n">
         <v>7.390000000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="K30" t="n">
@@ -8589,13 +8601,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8622,7 +8634,7 @@
       <c r="I31" t="n">
         <v>7.32</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K31" t="n">
@@ -8635,13 +8647,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8668,7 +8680,7 @@
       <c r="I32" t="n">
         <v>7.26</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K32" t="n">
@@ -8681,13 +8693,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8714,7 +8726,7 @@
       <c r="I33" t="n">
         <v>7.2</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K33" t="n">
@@ -8727,13 +8739,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8760,7 +8772,7 @@
       <c r="I34" t="n">
         <v>7.3</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="K34" t="n">
@@ -8773,13 +8785,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8806,7 +8818,7 @@
       <c r="I35" t="n">
         <v>7.58</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K35" t="n">
@@ -8819,13 +8831,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8852,7 +8864,7 @@
       <c r="I36" t="n">
         <v>7.859999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K36" t="n">
@@ -8865,13 +8877,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8898,7 +8910,7 @@
       <c r="I37" t="n">
         <v>8.18</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="K37" t="n">
@@ -8911,13 +8923,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8944,7 +8956,7 @@
       <c r="I38" t="n">
         <v>10.36</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K38" t="n">
@@ -8957,13 +8969,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8990,7 +9002,7 @@
       <c r="I39" t="n">
         <v>10.83</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K39" t="n">
@@ -9003,13 +9015,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9036,7 +9048,7 @@
       <c r="I40" t="n">
         <v>11.45</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K40" t="n">
@@ -9049,13 +9061,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9082,7 +9094,7 @@
       <c r="I41" t="n">
         <v>12.11</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="K41" t="n">
@@ -9095,13 +9107,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9128,7 +9140,7 @@
       <c r="I42" t="n">
         <v>10.71</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="K42" t="n">
@@ -9141,13 +9153,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9174,7 +9186,7 @@
       <c r="I43" t="n">
         <v>10.89</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K43" t="n">
@@ -9187,13 +9199,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9220,7 +9232,7 @@
       <c r="I44" t="n">
         <v>11.05</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K44" t="n">
@@ -9233,13 +9245,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9266,7 +9278,7 @@
       <c r="I45" t="n">
         <v>11.17</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="K45" t="n">
@@ -9279,13 +9291,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9312,7 +9324,7 @@
       <c r="I46" t="n">
         <v>11.39</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="K46" t="n">
@@ -9325,13 +9337,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9358,7 +9370,7 @@
       <c r="I47" t="n">
         <v>10.73</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K47" t="n">
@@ -9371,13 +9383,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9404,7 +9416,7 @@
       <c r="I48" t="n">
         <v>16.25</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K48" t="n">
@@ -9417,13 +9429,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9450,7 +9462,7 @@
       <c r="I49" t="n">
         <v>16.7</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="K49" t="n">
@@ -9463,13 +9475,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9496,7 +9508,7 @@
       <c r="I50" t="n">
         <v>16.96</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K50" t="n">
@@ -9509,13 +9521,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9542,7 +9554,7 @@
       <c r="I51" t="n">
         <v>19.11</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K51" t="n">
@@ -9555,13 +9567,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9588,7 +9600,7 @@
       <c r="I52" t="n">
         <v>13.14</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K52" t="n">
@@ -9601,13 +9613,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9634,7 +9646,7 @@
       <c r="I53" t="n">
         <v>13.05</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K53" t="n">
@@ -9647,13 +9659,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9680,7 +9692,7 @@
       <c r="I54" t="n">
         <v>12.7</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K54" t="n">
@@ -9693,13 +9705,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9726,7 +9738,7 @@
       <c r="I55" t="n">
         <v>11.83</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K55" t="n">
@@ -9739,13 +9751,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9772,7 +9784,7 @@
       <c r="I56" t="n">
         <v>12.79</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K56" t="n">
@@ -9785,13 +9797,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9818,7 +9830,7 @@
       <c r="I57" t="n">
         <v>13.27</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K57" t="n">
@@ -9831,13 +9843,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9864,7 +9876,7 @@
       <c r="I58" t="n">
         <v>13.85</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K58" t="n">
@@ -9877,13 +9889,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9910,7 +9922,7 @@
       <c r="I59" t="n">
         <v>14.6</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K59" t="n">
@@ -9923,13 +9935,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9956,7 +9968,7 @@
       <c r="I60" t="n">
         <v>14.57</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K60" t="n">
@@ -9969,13 +9981,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10002,7 +10014,7 @@
       <c r="I61" t="n">
         <v>14.39</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K61" t="n">
@@ -10015,13 +10027,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10048,7 +10060,7 @@
       <c r="I62" t="n">
         <v>12.79</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="K62" t="n">
@@ -10061,13 +10073,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10094,7 +10106,7 @@
       <c r="I63" t="n">
         <v>11.91</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -10107,13 +10119,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10140,7 +10152,7 @@
       <c r="I64" t="n">
         <v>11.94</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K64" t="n">
@@ -10153,13 +10165,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10186,7 +10198,7 @@
       <c r="I65" t="n">
         <v>11.83</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K65" t="n">
@@ -10199,13 +10211,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10232,7 +10244,7 @@
       <c r="I66" t="n">
         <v>13.74</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K66" t="n">
@@ -10245,13 +10257,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10278,7 +10290,7 @@
       <c r="I67" t="n">
         <v>14.15</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K67" t="n">
@@ -10291,13 +10303,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10324,7 +10336,7 @@
       <c r="I68" t="n">
         <v>14.61</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K68" t="n">
@@ -10337,13 +10349,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10370,7 +10382,7 @@
       <c r="I69" t="n">
         <v>15.47</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="K69" t="n">
@@ -10383,13 +10395,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10416,7 +10428,7 @@
       <c r="I70" t="n">
         <v>16.59</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="K70" t="n">
@@ -10429,13 +10441,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10462,7 +10474,7 @@
       <c r="I71" t="n">
         <v>17.21</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K71" t="n">
@@ -10475,13 +10487,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10508,7 +10520,7 @@
       <c r="I72" t="n">
         <v>18.17</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K72" t="n">
@@ -10545,52 +10557,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="C2" t="n">
@@ -10619,10 +10631,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10651,10 +10663,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40235</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40248</v>
       </c>
       <c r="C4" t="n">
@@ -10683,10 +10695,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10715,10 +10727,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -10747,10 +10759,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="C7" t="n">
@@ -10779,10 +10791,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40592</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="C8" t="n">
@@ -10811,10 +10823,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10843,10 +10855,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="C10" t="n">
@@ -10875,10 +10887,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="C11" t="n">
@@ -10907,10 +10919,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40956</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C12" t="n">
@@ -10939,10 +10951,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41038</v>
       </c>
       <c r="C13" t="n">
@@ -10971,10 +10983,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C14" t="n">
@@ -11003,10 +11015,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="C15" t="n">
@@ -11035,10 +11047,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C16" t="n">
@@ -11067,10 +11079,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="C17" t="n">
@@ -11099,10 +11111,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C18" t="n">
@@ -11131,10 +11143,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="C19" t="n">
@@ -11163,10 +11175,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41689</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="C20" t="n">
@@ -11195,10 +11207,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41749</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C21" t="n">
@@ -11227,10 +11239,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C22" t="n">
@@ -11259,10 +11271,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41936</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C23" t="n">
@@ -11291,10 +11303,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="C24" t="n">
@@ -11323,10 +11335,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C25" t="n">
@@ -11355,10 +11367,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42209</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11387,10 +11399,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C27" t="n">
@@ -11419,10 +11431,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="C28" t="n">
@@ -11451,10 +11463,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42482</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11483,10 +11495,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42573</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11515,10 +11527,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C31" t="n">
@@ -11547,10 +11559,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="C32" t="n">
@@ -11579,10 +11591,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11611,10 +11623,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11643,10 +11655,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="C35" t="n">
@@ -11675,10 +11687,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C36" t="n">
@@ -11707,10 +11719,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C37" t="n">
@@ -11739,10 +11751,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C38" t="n">
@@ -11771,10 +11783,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C39" t="n">
@@ -11803,10 +11815,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43504</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="C40" t="n">
@@ -11835,10 +11847,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43574</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C41" t="n">
@@ -11867,10 +11879,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43665</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C42" t="n">
@@ -11899,10 +11911,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43755</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="C43" t="n">
@@ -11931,10 +11943,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43867</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="C44" t="n">
@@ -11963,10 +11975,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43937</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -11995,10 +12007,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C46" t="n">
@@ -12027,10 +12039,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44120</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C47" t="n">
@@ -12059,10 +12071,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44232</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C48" t="n">
@@ -12091,10 +12103,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C49" t="n">
@@ -12123,10 +12135,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C50" t="n">
@@ -12155,10 +12167,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44484</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12187,10 +12199,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44596</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C52" t="n">
@@ -12219,10 +12231,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44664</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12251,10 +12263,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44755</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C54" t="n">
@@ -12283,10 +12295,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44851</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12315,10 +12327,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44960</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="C56" t="n">
@@ -12347,10 +12359,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45034</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C57" t="n">
@@ -12379,10 +12391,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12411,10 +12423,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45216</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12443,10 +12455,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45324</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="C60" t="n">
@@ -12475,10 +12487,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45397</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12507,10 +12519,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45488</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C62" t="n">
@@ -12539,10 +12551,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45581</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C63" t="n">
@@ -12571,10 +12583,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45691</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C64" t="n">
@@ -12603,10 +12615,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45763</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C65" t="n">
@@ -12635,10 +12647,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45853</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12667,10 +12679,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45944</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="C67" t="n">
@@ -12699,10 +12711,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="C68" t="n">
@@ -12731,10 +12743,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C69" t="n">
@@ -12763,10 +12775,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46223</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C70" t="n">
@@ -12813,12 +12825,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PNC.xlsx
+++ b/salidas/empresas/PNC.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>35.975830078125</v>
+        <v>35.9758186340332</v>
       </c>
       <c r="C2" t="n">
         <v>64.86000061035156</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>39.02095413208008</v>
+        <v>39.02095031738281</v>
       </c>
       <c r="C3" t="n">
         <v>70.34999847412109</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>37.33475112915039</v>
+        <v>37.33475875854492</v>
       </c>
       <c r="C4" t="n">
         <v>67.30999755859375</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>39.97009658813477</v>
+        <v>39.97007751464844</v>
       </c>
       <c r="C5" t="n">
         <v>71.47000122070312</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>38.53841018676758</v>
+        <v>38.53840255737305</v>
       </c>
       <c r="C6" t="n">
         <v>68.91000366210938</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>39.24304580688477</v>
+        <v>39.24306106567383</v>
       </c>
       <c r="C7" t="n">
         <v>70.16999816894531</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>39.92816925048828</v>
+        <v>39.92816162109375</v>
       </c>
       <c r="C8" t="n">
         <v>70.83999633789062</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>39.89997100830078</v>
+        <v>39.89996719360352</v>
       </c>
       <c r="C9" t="n">
         <v>70.79000091552734</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.82997512817383</v>
+        <v>40.82998275756836</v>
       </c>
       <c r="C10" t="n">
         <v>72.44000244140625</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>39.78303146362305</v>
+        <v>39.78303527832031</v>
       </c>
       <c r="C11" t="n">
         <v>70.02999877929688</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>40.1579704284668</v>
+        <v>40.15797805786133</v>
       </c>
       <c r="C12" t="n">
         <v>70.69000244140625</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>42.06106948852539</v>
+        <v>42.06105804443359</v>
       </c>
       <c r="C13" t="n">
         <v>74.04000091552734</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.21682357788086</v>
+        <v>42.21681976318359</v>
       </c>
       <c r="C14" t="n">
         <v>73.76999664306641</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>41.94211578369141</v>
+        <v>41.94211959838867</v>
       </c>
       <c r="C15" t="n">
         <v>73.29000091552734</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>41.18671417236328</v>
+        <v>41.18670654296875</v>
       </c>
       <c r="C16" t="n">
         <v>71.97000122070312</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>42.77543640136719</v>
+        <v>42.77544021606445</v>
       </c>
       <c r="C17" t="n">
         <v>74.09999847412109</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>42.60224533081055</v>
+        <v>42.60225296020508</v>
       </c>
       <c r="C18" t="n">
         <v>73.80000305175781</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>38.81690979003906</v>
+        <v>38.8169059753418</v>
       </c>
       <c r="C20" t="n">
         <v>66.65000152587891</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>40.98343276977539</v>
+        <v>40.98342895507812</v>
       </c>
       <c r="C21" t="n">
         <v>70.37000274658203</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>39.66139602661133</v>
+        <v>39.66139984130859</v>
       </c>
       <c r="C22" t="n">
         <v>68.09999847412109</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>43.01605606079102</v>
+        <v>43.01604843139648</v>
       </c>
       <c r="C24" t="n">
         <v>73.20999908447266</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>38.57401657104492</v>
+        <v>38.57402801513672</v>
       </c>
       <c r="C25" t="n">
         <v>65.65000152587891</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>36.46815872192383</v>
+        <v>36.46817779541016</v>
       </c>
       <c r="C27" t="n">
         <v>61.43000030517578</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>38.92588806152344</v>
+        <v>38.92590713500977</v>
       </c>
       <c r="C28" t="n">
         <v>65.56999969482422</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>41.58499908447266</v>
+        <v>41.58499526977539</v>
       </c>
       <c r="C29" t="n">
         <v>69.34999847412109</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>38.52684020996094</v>
+        <v>38.52684783935547</v>
       </c>
       <c r="C30" t="n">
         <v>64.25</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>34.23943328857422</v>
+        <v>34.23941802978516</v>
       </c>
       <c r="C31" t="n">
         <v>57.09999847412109</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>43.63714981079102</v>
+        <v>43.63714599609375</v>
       </c>
       <c r="C33" t="n">
         <v>71.94999694824219</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>45.30499267578125</v>
+        <v>45.30498504638672</v>
       </c>
       <c r="C34" t="n">
         <v>74.69999694824219</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>32.31235504150391</v>
+        <v>32.31233978271484</v>
       </c>
       <c r="C36" t="n">
         <v>52.77000045776367</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>30.00389099121094</v>
+        <v>30.0038890838623</v>
       </c>
       <c r="C37" t="n">
         <v>49</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>16.98453140258789</v>
+        <v>16.98452949523926</v>
       </c>
       <c r="C39" t="n">
         <v>27.34000015258789</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>28.38654899597168</v>
+        <v>28.38655281066895</v>
       </c>
       <c r="C42" t="n">
         <v>45.54999923706055</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>24.18621635437012</v>
+        <v>24.18621253967285</v>
       </c>
       <c r="C43" t="n">
         <v>38.81000137329102</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.90937232971191</v>
+        <v>22.90935707092285</v>
       </c>
       <c r="C44" t="n">
         <v>36.65999984741211</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>26.61510848999023</v>
+        <v>26.61511611938477</v>
       </c>
       <c r="C45" t="n">
         <v>42.59000015258789</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>30.3646068572998</v>
+        <v>30.36458969116211</v>
       </c>
       <c r="C46" t="n">
         <v>48.59000015258789</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>30.65033531188965</v>
+        <v>30.65033721923828</v>
       </c>
       <c r="C47" t="n">
         <v>48.93999862670898</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.0615348815918</v>
+        <v>33.06153869628906</v>
       </c>
       <c r="C49" t="n">
         <v>52.79000091552734</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>34.77624893188477</v>
+        <v>34.7762565612793</v>
       </c>
       <c r="C50" t="n">
         <v>55.43000030517578</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>33.72851181030273</v>
+        <v>33.72850799560547</v>
       </c>
       <c r="C51" t="n">
         <v>53.7599983215332</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>37.45519638061523</v>
+        <v>37.45520782470703</v>
       </c>
       <c r="C52" t="n">
         <v>59.70000076293945</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>42.2327995300293</v>
+        <v>42.23279571533203</v>
       </c>
       <c r="C53" t="n">
         <v>67.20999908447266</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>39.43027496337891</v>
+        <v>39.43027877807617</v>
       </c>
       <c r="C54" t="n">
         <v>62.75</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>35.50295639038086</v>
+        <v>35.50294876098633</v>
       </c>
       <c r="C55" t="n">
         <v>56.5</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>37.37933349609375</v>
+        <v>37.37933731079102</v>
       </c>
       <c r="C56" t="n">
         <v>59.38999938964844</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>32.09247589111328</v>
+        <v>32.09248352050781</v>
       </c>
       <c r="C57" t="n">
         <v>50.9900016784668</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>32.67151260375977</v>
+        <v>32.6715202331543</v>
       </c>
       <c r="C58" t="n">
         <v>51.90999984741211</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>33.98807144165039</v>
+        <v>33.98807525634766</v>
       </c>
       <c r="C59" t="n">
         <v>53.90000152587891</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>33.95653915405273</v>
+        <v>33.95654678344727</v>
       </c>
       <c r="C60" t="n">
         <v>53.84999847412109</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>38.28859329223633</v>
+        <v>38.28859710693359</v>
       </c>
       <c r="C61" t="n">
         <v>60.72000122070312</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>37.89598083496094</v>
+        <v>37.89598846435547</v>
       </c>
       <c r="C62" t="n">
         <v>60</v>
@@ -1790,7 +1790,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>39.78446197509766</v>
+        <v>39.78447723388672</v>
       </c>
       <c r="C64" t="n">
         <v>62.9900016784668</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>39.59551620483398</v>
+        <v>39.59551239013672</v>
       </c>
       <c r="C65" t="n">
         <v>62.34000015258789</v>
@@ -1848,7 +1848,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>39.64633560180664</v>
+        <v>39.64632034301758</v>
       </c>
       <c r="C66" t="n">
         <v>62.41999816894531</v>
@@ -1877,7 +1877,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>37.86155700683594</v>
+        <v>37.86154937744141</v>
       </c>
       <c r="C67" t="n">
         <v>59.61000061035156</v>
@@ -1906,7 +1906,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>34.69182968139648</v>
+        <v>34.69183731079102</v>
       </c>
       <c r="C68" t="n">
         <v>54.29000091552734</v>
@@ -1935,7 +1935,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>32.03995895385742</v>
+        <v>32.03995513916016</v>
       </c>
       <c r="C69" t="n">
         <v>50.13999938964844</v>
@@ -1964,7 +1964,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>30.79387855529785</v>
+        <v>30.79387664794922</v>
       </c>
       <c r="C70" t="n">
         <v>48.18999862670898</v>
@@ -1993,7 +1993,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>34.5576286315918</v>
+        <v>34.55760955810547</v>
       </c>
       <c r="C71" t="n">
         <v>53.70999908447266</v>
@@ -2051,7 +2051,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>37.10553741455078</v>
+        <v>37.10552978515625</v>
       </c>
       <c r="C73" t="n">
         <v>57.66999816894531</v>
@@ -2080,7 +2080,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>38.12625885009766</v>
+        <v>38.12625122070312</v>
       </c>
       <c r="C74" t="n">
         <v>58.91999816894531</v>
@@ -2109,7 +2109,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>38.51451873779297</v>
+        <v>38.5145149230957</v>
       </c>
       <c r="C75" t="n">
         <v>59.52000045776367</v>
@@ -2138,7 +2138,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>41.73052215576172</v>
+        <v>41.73052597045898</v>
       </c>
       <c r="C76" t="n">
         <v>64.48999786376953</v>
@@ -2167,7 +2167,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>43.18710708618164</v>
+        <v>43.18711471557617</v>
       </c>
       <c r="C77" t="n">
         <v>66.31999969482422</v>
@@ -2196,7 +2196,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>39.99626922607422</v>
+        <v>39.99627304077148</v>
       </c>
       <c r="C78" t="n">
         <v>61.41999816894531</v>
@@ -2254,7 +2254,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>38.74227523803711</v>
+        <v>38.7422981262207</v>
       </c>
       <c r="C80" t="n">
         <v>59.09999847412109</v>
@@ -2283,7 +2283,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>40.74822998046875</v>
+        <v>40.74822235107422</v>
       </c>
       <c r="C81" t="n">
         <v>62.15999984741211</v>
@@ -2312,7 +2312,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>41.36443328857422</v>
+        <v>41.36442565917969</v>
       </c>
       <c r="C82" t="n">
         <v>63.09999847412109</v>
@@ -2341,7 +2341,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>38.38872528076172</v>
+        <v>38.38872146606445</v>
       </c>
       <c r="C83" t="n">
         <v>58.20000076293945</v>
@@ -2370,7 +2370,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>37.02993774414062</v>
+        <v>37.02995300292969</v>
       </c>
       <c r="C84" t="n">
         <v>56.13999938964844</v>
@@ -2399,7 +2399,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>38.46128082275391</v>
+        <v>38.46128463745117</v>
       </c>
       <c r="C85" t="n">
         <v>58.31000137329102</v>
@@ -2428,7 +2428,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>41.03173446655273</v>
+        <v>41.0317268371582</v>
       </c>
       <c r="C86" t="n">
         <v>61.79999923706055</v>
@@ -2457,7 +2457,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.42345809936523</v>
+        <v>41.42344665527344</v>
       </c>
       <c r="C87" t="n">
         <v>62.38999938964844</v>
@@ -2486,7 +2486,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>44.15225219726562</v>
+        <v>44.15226364135742</v>
       </c>
       <c r="C88" t="n">
         <v>66.5</v>
@@ -2544,7 +2544,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>47.87790298461914</v>
+        <v>47.87791442871094</v>
       </c>
       <c r="C90" t="n">
         <v>71.63999938964844</v>
@@ -2573,7 +2573,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>48.73334884643555</v>
+        <v>48.73334503173828</v>
       </c>
       <c r="C91" t="n">
         <v>72.91999816894531</v>
@@ -2602,7 +2602,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>51.12676239013672</v>
+        <v>51.12673950195312</v>
       </c>
       <c r="C92" t="n">
         <v>76.05000305175781</v>
@@ -2631,7 +2631,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>48.58554840087891</v>
+        <v>48.58555603027344</v>
       </c>
       <c r="C93" t="n">
         <v>72.26999664306641</v>
@@ -2660,7 +2660,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>48.70655822753906</v>
+        <v>48.70656585693359</v>
       </c>
       <c r="C94" t="n">
         <v>72.44999694824219</v>
@@ -2689,7 +2689,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>49.7414436340332</v>
+        <v>49.74143600463867</v>
       </c>
       <c r="C95" t="n">
         <v>73.52999877929688</v>
@@ -2718,7 +2718,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>52.05498886108398</v>
+        <v>52.05500411987305</v>
       </c>
       <c r="C96" t="n">
         <v>76.94999694824219</v>
@@ -2776,7 +2776,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>54.34062576293945</v>
+        <v>54.34059906005859</v>
       </c>
       <c r="C98" t="n">
         <v>79.87999725341797</v>
@@ -2805,7 +2805,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>55.63314437866211</v>
+        <v>55.63313674926758</v>
       </c>
       <c r="C99" t="n">
         <v>81.77999877929688</v>
@@ -2834,7 +2834,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>59.1842041015625</v>
+        <v>59.18418884277344</v>
       </c>
       <c r="C100" t="n">
         <v>87</v>
@@ -2863,7 +2863,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>57.50634765625</v>
+        <v>57.50632476806641</v>
       </c>
       <c r="C101" t="n">
         <v>84.04000091552734</v>
@@ -2892,7 +2892,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>58.34800338745117</v>
+        <v>58.3480110168457</v>
       </c>
       <c r="C102" t="n">
         <v>85.26999664306641</v>
@@ -2921,7 +2921,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>60.93454742431641</v>
+        <v>60.93455505371094</v>
       </c>
       <c r="C103" t="n">
         <v>89.05000305175781</v>
@@ -2979,7 +2979,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>58.31223678588867</v>
+        <v>58.31224060058594</v>
       </c>
       <c r="C105" t="n">
         <v>84.75</v>
@@ -3008,7 +3008,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>58.8832893371582</v>
+        <v>58.88331604003906</v>
       </c>
       <c r="C106" t="n">
         <v>85.58000183105469</v>
@@ -3037,7 +3037,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>59.78631591796875</v>
+        <v>59.78629302978516</v>
       </c>
       <c r="C107" t="n">
         <v>86.38999938964844</v>
@@ -3066,7 +3066,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>60.53371047973633</v>
+        <v>60.53372573852539</v>
       </c>
       <c r="C108" t="n">
         <v>87.47000122070312</v>
@@ -3095,7 +3095,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>63.1358528137207</v>
+        <v>63.13584136962891</v>
       </c>
       <c r="C109" t="n">
         <v>91.23000335693359</v>
@@ -3124,7 +3124,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>58.83378219604492</v>
+        <v>58.83376312255859</v>
       </c>
       <c r="C110" t="n">
         <v>84.54000091552734</v>
@@ -3153,7 +3153,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>63.9975700378418</v>
+        <v>63.99753952026367</v>
       </c>
       <c r="C111" t="n">
         <v>91.95999908447266</v>
@@ -3182,7 +3182,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>64.88835144042969</v>
+        <v>64.88833618164062</v>
       </c>
       <c r="C112" t="n">
         <v>93.23999786376953</v>
@@ -3211,7 +3211,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>64.18768310546875</v>
+        <v>64.18769836425781</v>
       </c>
       <c r="C113" t="n">
         <v>91.73000335693359</v>
@@ -3240,7 +3240,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>66.95867919921875</v>
+        <v>66.95868682861328</v>
       </c>
       <c r="C114" t="n">
         <v>95.69000244140625</v>
@@ -3269,7 +3269,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>66.93070220947266</v>
+        <v>66.93070983886719</v>
       </c>
       <c r="C115" t="n">
         <v>95.65000152587891</v>
@@ -3298,7 +3298,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>69.06681823730469</v>
+        <v>69.06680297851562</v>
       </c>
       <c r="C116" t="n">
         <v>98.18000030517578</v>
@@ -3327,7 +3327,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>64.10031127929688</v>
+        <v>64.10031890869141</v>
       </c>
       <c r="C117" t="n">
         <v>91.12000274658203</v>
@@ -3356,7 +3356,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>62.74966049194336</v>
+        <v>62.74966430664062</v>
       </c>
       <c r="C118" t="n">
         <v>89.19999694824219</v>
@@ -3385,7 +3385,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>63.85835266113281</v>
+        <v>63.85837554931641</v>
       </c>
       <c r="C119" t="n">
         <v>90.26000213623047</v>
@@ -3414,7 +3414,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>67.57270812988281</v>
+        <v>67.57269287109375</v>
       </c>
       <c r="C120" t="n">
         <v>95.51000213623047</v>
@@ -3443,7 +3443,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>67.43121337890625</v>
+        <v>67.43119812011719</v>
       </c>
       <c r="C121" t="n">
         <v>95.30999755859375</v>
@@ -3472,7 +3472,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>61.66830444335938</v>
+        <v>61.66827774047852</v>
       </c>
       <c r="C122" t="n">
         <v>86.65000152587891</v>
@@ -3530,7 +3530,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>60.18795776367188</v>
+        <v>60.18796920776367</v>
       </c>
       <c r="C124" t="n">
         <v>84.56999969482422</v>
@@ -3559,7 +3559,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>62.85940170288086</v>
+        <v>62.85939407348633</v>
       </c>
       <c r="C125" t="n">
         <v>87.77999877929688</v>
@@ -3588,7 +3588,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>64.26295471191406</v>
+        <v>64.26293182373047</v>
       </c>
       <c r="C126" t="n">
         <v>89.73999786376953</v>
@@ -3617,7 +3617,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>58.28352737426758</v>
+        <v>58.28352355957031</v>
       </c>
       <c r="C127" t="n">
         <v>81.38999938964844</v>
@@ -3646,7 +3646,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>59.5849609375</v>
+        <v>59.58496475219727</v>
       </c>
       <c r="C128" t="n">
         <v>82.65000152587891</v>
@@ -3675,7 +3675,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>64.95589447021484</v>
+        <v>64.95592498779297</v>
       </c>
       <c r="C129" t="n">
         <v>90.09999847412109</v>
@@ -3704,7 +3704,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>64.94869232177734</v>
+        <v>64.94869995117188</v>
       </c>
       <c r="C130" t="n">
         <v>90.08999633789062</v>
@@ -3762,7 +3762,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>80.17965698242188</v>
+        <v>80.17966461181641</v>
       </c>
       <c r="C132" t="n">
         <v>110.5400009155273</v>
@@ -3791,7 +3791,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>84.83637237548828</v>
+        <v>84.83636474609375</v>
       </c>
       <c r="C133" t="n">
         <v>116.9599990844727</v>
@@ -3820,7 +3820,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>87.77299499511719</v>
+        <v>87.77296447753906</v>
       </c>
       <c r="C134" t="n">
         <v>120.4599990844727</v>
@@ -3849,7 +3849,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>92.70590972900391</v>
+        <v>92.70591735839844</v>
       </c>
       <c r="C135" t="n">
         <v>127.2300033569336</v>
@@ -3878,7 +3878,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>87.61265563964844</v>
+        <v>87.61264801025391</v>
       </c>
       <c r="C136" t="n">
         <v>120.2399978637695</v>
@@ -3907,7 +3907,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>87.66413879394531</v>
+        <v>87.66411590576172</v>
       </c>
       <c r="C137" t="n">
         <v>119.75</v>
@@ -3936,7 +3936,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>86.89546966552734</v>
+        <v>86.89547729492188</v>
       </c>
       <c r="C138" t="n">
         <v>118.6999969482422</v>
@@ -3994,7 +3994,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>94.84841918945312</v>
+        <v>94.84841156005859</v>
       </c>
       <c r="C140" t="n">
         <v>128.8000030517578</v>
@@ -4081,7 +4081,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>101.3002853393555</v>
+        <v>101.3003158569336</v>
       </c>
       <c r="C143" t="n">
         <v>136.7899932861328</v>
@@ -4110,7 +4110,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>104.0921859741211</v>
+        <v>104.0921936035156</v>
       </c>
       <c r="C144" t="n">
         <v>140.5599975585938</v>
@@ -4139,7 +4139,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>106.8544769287109</v>
+        <v>106.8544616699219</v>
       </c>
       <c r="C145" t="n">
         <v>144.2899932861328</v>
@@ -4168,7 +4168,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>117.6031646728516</v>
+        <v>117.603157043457</v>
       </c>
       <c r="C146" t="n">
         <v>158.0200042724609</v>
@@ -4197,7 +4197,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>117.3352355957031</v>
+        <v>117.3352508544922</v>
       </c>
       <c r="C147" t="n">
         <v>157.6600036621094</v>
@@ -4226,7 +4226,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>112.5572662353516</v>
+        <v>112.5573043823242</v>
       </c>
       <c r="C148" t="n">
         <v>151.2400054931641</v>
@@ -4255,7 +4255,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>108.9029006958008</v>
+        <v>108.9029159545898</v>
       </c>
       <c r="C149" t="n">
         <v>145.6100006103516</v>
@@ -4284,7 +4284,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>107.2574996948242</v>
+        <v>107.2574844360352</v>
       </c>
       <c r="C150" t="n">
         <v>143.4100036621094</v>
@@ -4313,7 +4313,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>101.0423889160156</v>
+        <v>101.0423736572266</v>
       </c>
       <c r="C151" t="n">
         <v>135.1000061035156</v>
@@ -4342,7 +4342,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>109.0686187744141</v>
+        <v>109.0686340332031</v>
       </c>
       <c r="C152" t="n">
         <v>144.8300018310547</v>
@@ -4400,7 +4400,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>102.5620040893555</v>
+        <v>102.5619964599609</v>
       </c>
       <c r="C154" t="n">
         <v>136.1900024414062</v>
@@ -4429,7 +4429,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>97.50075531005859</v>
+        <v>97.50077056884766</v>
       </c>
       <c r="C155" t="n">
         <v>128.4900054931641</v>
@@ -4458,7 +4458,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>103.0325622558594</v>
+        <v>103.0325241088867</v>
       </c>
       <c r="C156" t="n">
         <v>135.7799987792969</v>
@@ -4516,7 +4516,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>93.82028961181641</v>
+        <v>93.82028198242188</v>
       </c>
       <c r="C158" t="n">
         <v>122.6699981689453</v>
@@ -4545,7 +4545,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>96.38246154785156</v>
+        <v>96.38241577148438</v>
       </c>
       <c r="C159" t="n">
         <v>126.0199966430664</v>
@@ -4574,7 +4574,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>93.81266021728516</v>
+        <v>93.81263732910156</v>
       </c>
       <c r="C160" t="n">
         <v>122.6600036621094</v>
@@ -4632,7 +4632,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>98.03262329101562</v>
+        <v>98.03263854980469</v>
       </c>
       <c r="C162" t="n">
         <v>127.2600021362305</v>
@@ -4661,7 +4661,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>105.7513580322266</v>
+        <v>105.7513732910156</v>
       </c>
       <c r="C163" t="n">
         <v>137.2799987792969</v>
@@ -4690,7 +4690,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>110.9944686889648</v>
+        <v>110.9944458007812</v>
       </c>
       <c r="C164" t="n">
         <v>142.8999938964844</v>
@@ -4719,7 +4719,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>100.1435699462891</v>
+        <v>100.1435775756836</v>
       </c>
       <c r="C165" t="n">
         <v>128.9299926757812</v>
@@ -4748,7 +4748,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>108.8662643432617</v>
+        <v>108.8662338256836</v>
       </c>
       <c r="C166" t="n">
         <v>140.1600036621094</v>
@@ -4777,7 +4777,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>114.8772354125977</v>
+        <v>114.8772277832031</v>
       </c>
       <c r="C167" t="n">
         <v>146.6999969482422</v>
@@ -4806,7 +4806,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>119.9750518798828</v>
+        <v>119.9750747680664</v>
       </c>
       <c r="C168" t="n">
         <v>153.2100067138672</v>
@@ -4835,7 +4835,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>125.00244140625</v>
+        <v>125.0024185180664</v>
       </c>
       <c r="C169" t="n">
         <v>159.6300048828125</v>
@@ -4893,7 +4893,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>99.72512054443359</v>
+        <v>99.72510528564453</v>
       </c>
       <c r="C171" t="n">
         <v>126.4000015258789</v>
@@ -4922,7 +4922,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>75.51968383789062</v>
+        <v>75.51967620849609</v>
       </c>
       <c r="C172" t="n">
         <v>95.72000122070312</v>
@@ -4980,7 +4980,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>91.02587890625</v>
+        <v>91.02588653564453</v>
       </c>
       <c r="C174" t="n">
         <v>114.0400009155273</v>
@@ -5009,7 +5009,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>83.97784423828125</v>
+        <v>83.97782135009766</v>
       </c>
       <c r="C175" t="n">
         <v>105.2099990844727</v>
@@ -5067,7 +5067,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>89.75079345703125</v>
+        <v>89.75078582763672</v>
       </c>
       <c r="C177" t="n">
         <v>111.1999969482422</v>
@@ -5096,7 +5096,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>88.70960998535156</v>
+        <v>88.7095947265625</v>
       </c>
       <c r="C178" t="n">
         <v>109.9100036621094</v>
@@ -5125,7 +5125,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>91.255126953125</v>
+        <v>91.25511932373047</v>
       </c>
       <c r="C179" t="n">
         <v>111.879997253418</v>
@@ -5183,7 +5183,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>121.5320816040039</v>
+        <v>121.532112121582</v>
       </c>
       <c r="C181" t="n">
         <v>149</v>
@@ -5212,7 +5212,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>117.9019241333008</v>
+        <v>117.9018783569336</v>
       </c>
       <c r="C182" t="n">
         <v>143.5200042724609</v>
@@ -5241,7 +5241,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>138.3079833984375</v>
+        <v>138.3079986572266</v>
       </c>
       <c r="C183" t="n">
         <v>168.3600006103516</v>
@@ -5270,7 +5270,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>144.0995635986328</v>
+        <v>144.0995483398438</v>
       </c>
       <c r="C184" t="n">
         <v>175.4100036621094</v>
@@ -5328,7 +5328,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>160.9620513916016</v>
+        <v>160.9620819091797</v>
       </c>
       <c r="C186" t="n">
         <v>194.6799926757812</v>
@@ -5357,7 +5357,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>157.7209930419922</v>
+        <v>157.7209625244141</v>
       </c>
       <c r="C187" t="n">
         <v>190.7599945068359</v>
@@ -5386,7 +5386,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>151.8248596191406</v>
+        <v>151.8248291015625</v>
       </c>
       <c r="C188" t="n">
         <v>182.4100036621094</v>
@@ -5444,7 +5444,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>162.8365631103516</v>
+        <v>162.8365020751953</v>
       </c>
       <c r="C190" t="n">
         <v>195.6399993896484</v>
@@ -5502,7 +5502,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>164.9906768798828</v>
+        <v>164.9907073974609</v>
       </c>
       <c r="C192" t="n">
         <v>197</v>
@@ -5531,7 +5531,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>167.9387512207031</v>
+        <v>167.9387664794922</v>
       </c>
       <c r="C193" t="n">
         <v>200.5200042724609</v>
@@ -5560,7 +5560,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>173.4775695800781</v>
+        <v>173.4775543212891</v>
       </c>
       <c r="C194" t="n">
         <v>205.9900054931641</v>
@@ -5589,7 +5589,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>167.8013458251953</v>
+        <v>167.8013763427734</v>
       </c>
       <c r="C195" t="n">
         <v>199.25</v>
@@ -5647,7 +5647,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>141.0334625244141</v>
+        <v>141.0334777832031</v>
       </c>
       <c r="C197" t="n">
         <v>166.1000061035156</v>
@@ -5676,7 +5676,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>148.9384613037109</v>
+        <v>148.9384765625</v>
       </c>
       <c r="C198" t="n">
         <v>175.4100036621094</v>
@@ -5705,7 +5705,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>133.9605712890625</v>
+        <v>133.9605560302734</v>
       </c>
       <c r="C199" t="n">
         <v>157.7700042724609</v>
@@ -5734,7 +5734,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>142.2291259765625</v>
+        <v>142.2291564941406</v>
       </c>
       <c r="C200" t="n">
         <v>165.9400024414062</v>
@@ -5763,7 +5763,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>135.4236907958984</v>
+        <v>135.4237213134766</v>
       </c>
       <c r="C201" t="n">
         <v>158</v>
@@ -5792,7 +5792,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>128.0696716308594</v>
+        <v>128.0696411132812</v>
       </c>
       <c r="C202" t="n">
         <v>149.4199981689453</v>
@@ -5879,7 +5879,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>136.7128753662109</v>
+        <v>136.7128448486328</v>
       </c>
       <c r="C205" t="n">
         <v>157.9400024414062</v>
@@ -5908,7 +5908,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>144.4799041748047</v>
+        <v>144.4799194335938</v>
       </c>
       <c r="C206" t="n">
         <v>165.4299926757812</v>
@@ -5966,7 +5966,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>111.0040435791016</v>
+        <v>111.0040512084961</v>
       </c>
       <c r="C208" t="n">
         <v>127.0999984741211</v>
@@ -5995,7 +5995,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>115.1729354858398</v>
+        <v>115.1729278564453</v>
       </c>
       <c r="C209" t="n">
         <v>130.25</v>
@@ -6082,7 +6082,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>122.5073547363281</v>
+        <v>122.5073318481445</v>
       </c>
       <c r="C212" t="n">
         <v>136.8899993896484</v>
@@ -6111,7 +6111,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>108.0452423095703</v>
+        <v>108.0452346801758</v>
       </c>
       <c r="C213" t="n">
         <v>120.7300033569336</v>
@@ -6140,7 +6140,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>109.8708801269531</v>
+        <v>109.8708953857422</v>
       </c>
       <c r="C214" t="n">
         <v>122.7699966430664</v>
@@ -6198,7 +6198,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>121.4790191650391</v>
+        <v>121.4790115356445</v>
       </c>
       <c r="C216" t="n">
         <v>133.9600067138672</v>
@@ -6314,7 +6314,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>148.0481414794922</v>
+        <v>148.0481719970703</v>
       </c>
       <c r="C220" t="n">
         <v>161.6000061035156</v>
@@ -6343,7 +6343,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>141.8343505859375</v>
+        <v>141.8343811035156</v>
       </c>
       <c r="C221" t="n">
         <v>153.2599945068359</v>
@@ -6372,7 +6372,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>145.6564788818359</v>
+        <v>145.6564636230469</v>
       </c>
       <c r="C222" t="n">
         <v>157.3899993896484</v>
@@ -6488,7 +6488,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>172.7086944580078</v>
+        <v>172.7087249755859</v>
       </c>
       <c r="C226" t="n">
         <v>184.8500061035156</v>
@@ -6517,7 +6517,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>177.3796234130859</v>
+        <v>177.3795928955078</v>
       </c>
       <c r="C227" t="n">
         <v>188.2700042724609</v>
@@ -6546,7 +6546,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>202.2996215820312</v>
+        <v>202.2996368408203</v>
       </c>
       <c r="C228" t="n">
         <v>214.7200012207031</v>
@@ -6575,7 +6575,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>181.6946716308594</v>
+        <v>181.6947021484375</v>
       </c>
       <c r="C229" t="n">
         <v>192.8500061035156</v>
@@ -6604,7 +6604,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>190.8867034912109</v>
+        <v>190.88671875</v>
       </c>
       <c r="C230" t="n">
         <v>200.9499969482422</v>
@@ -6633,7 +6633,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>182.3089141845703</v>
+        <v>182.3088989257812</v>
       </c>
       <c r="C231" t="n">
         <v>191.9199981689453</v>
@@ -6662,7 +6662,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>166.9676971435547</v>
+        <v>166.9677124023438</v>
       </c>
       <c r="C232" t="n">
         <v>175.7700042724609</v>
@@ -6749,7 +6749,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>178.9266967773438</v>
+        <v>178.9267120361328</v>
       </c>
       <c r="C235" t="n">
         <v>186.4199981689453</v>
@@ -6778,7 +6778,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>184.2084350585938</v>
+        <v>184.2084503173828</v>
       </c>
       <c r="C236" t="n">
         <v>190.2700042724609</v>
@@ -6807,7 +6807,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>200.8314514160156</v>
+        <v>200.8314361572266</v>
       </c>
       <c r="C237" t="n">
         <v>207.4400024414062</v>
